--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486994_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486994_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8589</v>
+        <v>4.3489</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1585</v>
+        <v>5.2631</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2996</v>
+        <v>-0.9142</v>
       </c>
       <c r="G2" t="n">
         <v>5.2495</v>
@@ -610,13 +610,13 @@
         <v>1.0267</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0066</v>
+        <v>0.4834</v>
       </c>
       <c r="T2" t="n">
-        <v>0.244</v>
+        <v>0.3486</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2506</v>
+        <v>0.1348</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1786</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8843</v>
+        <v>1.0935</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6065</v>
+        <v>-0.3973</v>
       </c>
       <c r="F3" t="n">
         <v>1.4908</v>
@@ -688,10 +688,10 @@
         <v>0.4107</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0232</v>
+        <v>0.186</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2635</v>
+        <v>-0.0543</v>
       </c>
       <c r="U3" t="n">
         <v>0.2403</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>F. HERNANDEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1692</v>
+        <v>-0.8042</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2279</v>
+        <v>-1.8543</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3971</v>
+        <v>1.0501</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9954</v>
+        <v>-1.6308</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9568</v>
+        <v>-0.5545</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.9522</v>
+        <v>-1.0763</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1967</v>
+        <v>-1.6759</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9217</v>
+        <v>-0.8073</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1184</v>
+        <v>-0.8686</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7987</v>
+        <v>0.0452</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0351</v>
+        <v>0.2528</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8338</v>
+        <v>-0.2077</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2855</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8481</v>
+        <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6365</v>
+        <v>-0.1037</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8827</v>
+        <v>-0.4186</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7539</v>
+        <v>0.3149</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0345</v>
+        <v>0.1088</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3716</v>
+        <v>0.2402</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4061</v>
+        <v>-0.1314</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. KABASELE KASONGA</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.168</v>
+        <v>-0.9363</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0584</v>
+        <v>-1.5907</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1096</v>
+        <v>0.6544</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.485</v>
+        <v>0.6292</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8854</v>
+        <v>2.6213</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5997</v>
+        <v>-1.992</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7439</v>
+        <v>0.4783</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8623</v>
+        <v>2.0313</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1184</v>
+        <v>-1.5529</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7411</v>
+        <v>0.1509</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0231</v>
+        <v>0.59</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7181</v>
+        <v>-0.4391</v>
       </c>
       <c r="P5" t="n">
         <v>-1.6427</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2588</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3043</v>
+        <v>0.2432</v>
       </c>
       <c r="T5" t="n">
-        <v>2.704</v>
+        <v>-0.0156</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.2588</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3445</v>
+        <v>-0.1659</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5848</v>
+        <v>-0.1659</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. HERNANDEZ MARTINEZ</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2309</v>
+        <v>-1.1378</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5478</v>
+        <v>-0.1005</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3169</v>
+        <v>-1.0373</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6308</v>
+        <v>-0.5072</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5545</v>
+        <v>0.1427</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0763</v>
+        <v>-0.6498</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6759</v>
+        <v>0.0584</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8073</v>
+        <v>0.0584</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8686</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0452</v>
+        <v>-0.5656</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2528</v>
+        <v>0.0843</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2077</v>
+        <v>-0.6498</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5304</v>
+        <v>-0.1501</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1121</v>
+        <v>-0.1589</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5817</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1088</v>
+        <v>-0.4805</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1314</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3313</v>
+        <v>-1.2556</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2051</v>
+        <v>-2.2081</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1262</v>
+        <v>0.9525</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5072</v>
+        <v>-0.9954</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1427</v>
+        <v>0.9568</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6498</v>
+        <v>-1.9522</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0584</v>
+        <v>-0.1967</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0584</v>
+        <v>0.9217</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.1184</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5656</v>
+        <v>-0.7987</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0843</v>
+        <v>0.0351</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6498</v>
+        <v>-0.8338</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.8481</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3437</v>
+        <v>1.2117</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2635</v>
+        <v>0.9025</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.3092</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4805</v>
+        <v>-0.0345</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3716</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4805</v>
+        <v>-0.4061</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. ZAMORA MAÑA</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6953</v>
+        <v>-1.6281</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6151</v>
+        <v>-0.058</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-1.57</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4186</v>
+        <v>1.2941</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1688</v>
+        <v>1.3044</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2499</v>
+        <v>-0.0104</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.627</v>
+        <v>1.2198</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1363</v>
+        <v>1.0225</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7633</v>
+        <v>0.1973</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7917</v>
+        <v>0.0743</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.305</v>
+        <v>0.2819</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4866</v>
+        <v>-0.2077</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3394</v>
+        <v>-0.4417</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0386</v>
+        <v>-0.4031</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3007</v>
+        <v>-0.0386</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.6591</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.8377</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>U. ZAMORA MAÑA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7121</v>
+        <v>-1.8139</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2183</v>
+        <v>-1.6151</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5062</v>
+        <v>-0.1988</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6292</v>
+        <v>-1.4186</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6213</v>
+        <v>-0.1688</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.992</v>
+        <v>-1.2499</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4783</v>
+        <v>-0.627</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0313</v>
+        <v>0.1363</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5529</v>
+        <v>-0.7633</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1509</v>
+        <v>-0.7917</v>
       </c>
       <c r="N9" t="n">
-        <v>0.59</v>
+        <v>-0.305</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4391</v>
+        <v>-0.4866</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6427</v>
+        <v>-0.616</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
         <v>0.4107</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5327</v>
+        <v>0.2208</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6433</v>
+        <v>0.0386</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1106</v>
+        <v>0.1822</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1659</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0078</v>
+        <v>-2.3522</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4377</v>
+        <v>-0.6832</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.57</v>
+        <v>-1.669</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2941</v>
+        <v>1.0631</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3044</v>
+        <v>1.8133</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0104</v>
+        <v>-0.7502</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2198</v>
+        <v>1.936</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0225</v>
+        <v>2.1996</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1973</v>
+        <v>-0.2636</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0743</v>
+        <v>-0.8729</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2819</v>
+        <v>-0.3863</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2077</v>
+        <v>-0.4866</v>
       </c>
       <c r="P10" t="n">
         <v>-0.8214</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>-2.2588</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8214</v>
+        <v>-0.0708</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7827</v>
+        <v>-0.3605</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0386</v>
+        <v>0.2897</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6591</v>
+        <v>-2.5232</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.8377</v>
+        <v>-2.5232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0753</v>
+        <v>-2.7138</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3767</v>
+        <v>-1.2666</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6986</v>
+        <v>-1.4472</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0631</v>
+        <v>-1.04</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8133</v>
+        <v>1.1808</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7502</v>
+        <v>-2.2208</v>
       </c>
       <c r="J11" t="n">
-        <v>1.936</v>
+        <v>-1.0223</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1996</v>
+        <v>0.8988</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2636</v>
+        <v>-1.9212</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8729</v>
+        <v>-0.0177</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3863</v>
+        <v>0.2819</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4866</v>
+        <v>-0.2996</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8214</v>
+        <v>0.8214</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7939000000000001</v>
+        <v>0.2683</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.054</v>
+        <v>-0.0389</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2601</v>
+        <v>0.3072</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.5232</v>
+        <v>-2.7634</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5232</v>
+        <v>-2.7634</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>H. KABASELE KASONGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0918</v>
+        <v>-2.8713</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4371</v>
+        <v>-1.732</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6547</v>
+        <v>-1.1392</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.04</v>
+        <v>-1.485</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1808</v>
+        <v>-0.8854</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2208</v>
+        <v>-0.5997</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0223</v>
+        <v>-0.7439</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8988</v>
+        <v>-0.8623</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9212</v>
+        <v>0.1184</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0177</v>
+        <v>-0.7411</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2819</v>
+        <v>-0.0231</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2996</v>
+        <v>-0.7181</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8214</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2053</v>
+        <v>-2.2588</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1097</v>
+        <v>1.6011</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2094</v>
+        <v>1.0304</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0997</v>
+        <v>0.5707</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7634</v>
+        <v>-1.3445</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7634</v>
+        <v>-1.5848</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.4001</v>
+        <v>-10.0708</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.5721</v>
+        <v>-6.2427</v>
       </c>
       <c r="F13" t="n">
         <v>-3.827900000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6557</v>
+        <v>1.655700000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>9.326400000000001</v>
+        <v>9.326399999999998</v>
       </c>
       <c r="I13" t="n">
         <v>-7.6708</v>
@@ -1444,10 +1444,10 @@
         <v>4.99</v>
       </c>
       <c r="K13" t="n">
-        <v>8.0322</v>
+        <v>8.032200000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.0422</v>
+        <v>-3.042200000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-3.3344</v>
@@ -1456,10 +1456,10 @@
         <v>1.2942</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.628699999999999</v>
+        <v>-4.6287</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.133399999999999</v>
+        <v>-5.1334</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.374</v>
@@ -1468,10 +1468,10 @@
         <v>9.240500000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1186</v>
+        <v>3.4482</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5408000000000004</v>
+        <v>0.8701999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>2.5779</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0125</v>
+        <v>4.4291</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6831</v>
+        <v>3.2061</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3295</v>
+        <v>1.223</v>
       </c>
       <c r="G14" t="n">
         <v>1.6184</v>
@@ -1546,13 +1546,13 @@
         <v>2.8748</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6593</v>
+        <v>-1.2427</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4415</v>
+        <v>-0.9184</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2179</v>
+        <v>-0.3243</v>
       </c>
       <c r="V14" t="n">
         <v>1.1786</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2121</v>
+        <v>2.8006</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7427</v>
+        <v>1.4289</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4694</v>
+        <v>1.3717</v>
       </c>
       <c r="G15" t="n">
         <v>0.8238</v>
@@ -1624,13 +1624,13 @@
         <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3185</v>
+        <v>-0.093</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0545</v>
+        <v>-0.3683</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3729</v>
+        <v>0.2753</v>
       </c>
       <c r="V15" t="n">
         <v>1.6591</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5667</v>
+        <v>2.6878</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.826</v>
+        <v>1.0212</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3927</v>
+        <v>1.6665</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1438</v>
+        <v>-0.3893</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3205</v>
+        <v>-1.6155</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1766</v>
+        <v>1.2261</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4027</v>
+        <v>-0.4091</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6</v>
+        <v>-0.8428</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1973</v>
+        <v>0.4338</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7411</v>
+        <v>0.0197</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7204</v>
+        <v>-0.7726</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0207</v>
+        <v>0.7924</v>
       </c>
       <c r="P16" t="n">
         <v>2.0534</v>
@@ -1702,22 +1702,22 @@
         <v>2.0534</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8974</v>
+        <v>-0.8757</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2749</v>
+        <v>-0.469</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6225</v>
+        <v>-0.4066</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2402</v>
+        <v>1.8993</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6982</v>
+        <v>1.8993</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0872</v>
+        <v>2.279</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2575</v>
+        <v>2.1529</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1703</v>
+        <v>0.1261</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6884</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4184</v>
+        <v>0.6102</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4997</v>
+        <v>0.3951</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0813</v>
+        <v>0.2151</v>
       </c>
       <c r="V17" t="n">
         <v>2.3573</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>V. MUÑOZ QUIÑONES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8439</v>
+        <v>1.3968</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8120000000000001</v>
+        <v>-1.4536</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0319</v>
+        <v>2.8504</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3893</v>
+        <v>-1.1438</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6155</v>
+        <v>-1.3205</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2261</v>
+        <v>0.1766</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4091</v>
+        <v>-0.4027</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8428</v>
+        <v>-0.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4338</v>
+        <v>0.1973</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0197</v>
+        <v>-0.7411</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7726</v>
+        <v>-0.7204</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7924</v>
+        <v>-0.0207</v>
       </c>
       <c r="P18" t="n">
         <v>2.0534</v>
@@ -1858,22 +1858,22 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7195</v>
+        <v>0.7274</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6782</v>
+        <v>-0.3527</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0413</v>
+        <v>1.0802</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8993</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8993</v>
+        <v>-0.6982</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8853</v>
+        <v>1.2374</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9726</v>
+        <v>1.6003</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0873</v>
+        <v>-0.3629</v>
       </c>
       <c r="G19" t="n">
         <v>1.2217</v>
@@ -1936,13 +1936,13 @@
         <v>2.0534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6833</v>
+        <v>-0.3312</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9145</v>
+        <v>-0.2869</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2312</v>
+        <v>-0.0443</v>
       </c>
       <c r="V19" t="n">
         <v>3.427</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4711</v>
+        <v>0.0105</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8639</v>
+        <v>-0.9575</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3928</v>
+        <v>0.968</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0704</v>
+        <v>0.5886</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0307</v>
+        <v>-2.0112</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9603</v>
+        <v>2.5997</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.8567</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3363</v>
+        <v>-2.0142</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2629</v>
+        <v>1.1575</v>
       </c>
       <c r="M20" t="n">
+        <v>1.4452</v>
+      </c>
+      <c r="N20" t="n">
         <v>0.003</v>
       </c>
-      <c r="N20" t="n">
-        <v>-0.6943</v>
-      </c>
       <c r="O20" t="n">
-        <v>0.6974</v>
+        <v>1.4422</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2153</v>
+        <v>-0.2208</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2362</v>
+        <v>-0.1008</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0209</v>
+        <v>-0.12</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0217</v>
+        <v>-0.2891</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3759</v>
+        <v>1.0901</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3542</v>
+        <v>-1.3792</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5886</v>
+        <v>-2.3298</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0112</v>
+        <v>-0.117</v>
       </c>
       <c r="I21" t="n">
-        <v>2.5997</v>
+        <v>-2.2128</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8567</v>
+        <v>-0.2705</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0142</v>
+        <v>0.9928</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1575</v>
+        <v>-1.2633</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4452</v>
+        <v>-2.0592</v>
       </c>
       <c r="N21" t="n">
-        <v>0.003</v>
+        <v>-1.1098</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4422</v>
+        <v>-0.9495</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.253</v>
+        <v>-0.37</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5192</v>
+        <v>-0.2985</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7337</v>
+        <v>-0.0716</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1786</v>
+        <v>1.1786</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1786</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1643</v>
+        <v>-0.7116</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6717</v>
+        <v>-1.2823</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.836</v>
+        <v>0.5706</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3298</v>
+        <v>-0.0704</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.117</v>
+        <v>-2.0307</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2128</v>
+        <v>1.9603</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2705</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9928</v>
+        <v>-1.3363</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2633</v>
+        <v>1.2629</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0592</v>
+        <v>0.003</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1098</v>
+        <v>-0.6943</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9495</v>
+        <v>0.6974</v>
       </c>
       <c r="P22" t="n">
-        <v>1.2321</v>
+        <v>-0.616</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2452</v>
+        <v>-0.0252</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7169</v>
+        <v>-0.1822</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5284</v>
+        <v>0.157</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6591</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5506</v>
+        <v>-2.0457</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.246</v>
+        <v>-2.9782</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6953</v>
+        <v>0.9325</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2863</v>
@@ -2248,13 +2248,13 @@
         <v>0.4107</v>
       </c>
       <c r="S23" t="n">
-        <v>0.592</v>
+        <v>0.0969</v>
       </c>
       <c r="T23" t="n">
-        <v>0.736</v>
+        <v>0.0038</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.144</v>
+        <v>0.0931</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2402</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.7948</v>
       </c>
       <c r="E24" t="n">
-        <v>3.8278</v>
+        <v>3.8279</v>
       </c>
       <c r="F24" t="n">
-        <v>6.5722</v>
+        <v>7.966699999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6555</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.326599999999999</v>
+        <v>-9.326600000000001</v>
       </c>
       <c r="I24" t="n">
         <v>7.6708</v>
@@ -2305,10 +2305,10 @@
         <v>-1.2942</v>
       </c>
       <c r="L24" t="n">
-        <v>4.628699999999999</v>
+        <v>4.6287</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.990100000000001</v>
+        <v>-4.9901</v>
       </c>
       <c r="N24" t="n">
         <v>-8.0322</v>
@@ -2317,7 +2317,7 @@
         <v>3.0422</v>
       </c>
       <c r="P24" t="n">
-        <v>5.1337</v>
+        <v>5.133700000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-9.240399999999999</v>
@@ -2326,13 +2326,13 @@
         <v>14.374</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.1187</v>
+        <v>-1.7241</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.578</v>
+        <v>-2.5779</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5408999999999998</v>
+        <v>0.8539000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>10.0409</v>
@@ -2341,7 +2341,7 @@
         <v>12.3118</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2709</v>
+        <v>-2.270900000000001</v>
       </c>
     </row>
   </sheetData>
